--- a/results/682_z23/5_quantification/682_z23_quantification.xlsx
+++ b/results/682_z23/5_quantification/682_z23_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>6.6364</v>
+        <v>5.9091</v>
       </c>
       <c r="D12" t="n">
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0136</v>
+        <v>2.0715</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>300.0909</v>
+        <v>315.1818</v>
       </c>
       <c r="D13" t="n">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="E13" t="n">
-        <v>73.16759999999999</v>
+        <v>82.5843</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>819.1818</v>
+        <v>864.1818</v>
       </c>
       <c r="D14" t="n">
-        <v>824</v>
+        <v>883</v>
       </c>
       <c r="E14" t="n">
-        <v>137.9977</v>
+        <v>157.884</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1767.0326</v>
+        <v>2076.5144</v>
       </c>
       <c r="D15" t="n">
-        <v>1286.9575</v>
+        <v>1597.8692</v>
       </c>
       <c r="E15" t="n">
-        <v>1121.2217</v>
+        <v>1461.6153</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>79.1818</v>
+        <v>97.36360000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
-        <v>52.7443</v>
+        <v>70.6049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.8818</v>
+        <v>22.0665</v>
       </c>
       <c r="D17" t="n">
-        <v>23.7818</v>
+        <v>21.1756</v>
       </c>
       <c r="E17" t="n">
-        <v>2.1918</v>
+        <v>2.5685</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03400888</v>
+        <v>0.03580719</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03296322</v>
+        <v>0.03527643</v>
       </c>
       <c r="E23" t="n">
-        <v>0.009277860000000001</v>
+        <v>0.0108291</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0367476</v>
+        <v>0.03881081</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03645267</v>
+        <v>0.03884808</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00652245</v>
+        <v>0.00773588</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.0582</v>
+        <v>2.7497</v>
       </c>
       <c r="D25" t="n">
-        <v>2.8549</v>
+        <v>2.6998</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9582000000000001</v>
+        <v>1.0704</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>238.4545</v>
+        <v>256.9091</v>
       </c>
       <c r="D26" t="n">
-        <v>221</v>
+        <v>249</v>
       </c>
       <c r="E26" t="n">
-        <v>84.8167</v>
+        <v>94.1652</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>519.5454999999999</v>
+        <v>596.4545000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>547</v>
+        <v>591</v>
       </c>
       <c r="E27" t="n">
-        <v>170.8212</v>
+        <v>215.5701</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>337.4499</v>
+        <v>356.2859</v>
       </c>
       <c r="D28" t="n">
-        <v>363.0782</v>
+        <v>372.0782</v>
       </c>
       <c r="E28" t="n">
-        <v>81.5864</v>
+        <v>92.25920000000001</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>924.8247</v>
+        <v>975.7318</v>
       </c>
       <c r="D29" t="n">
-        <v>946.8792999999999</v>
+        <v>994.3229</v>
       </c>
       <c r="E29" t="n">
-        <v>148.656</v>
+        <v>173.3484</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1227,7 +1227,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="n">
-        <v>2.0181</v>
+        <v>2.2523</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1253,10 +1253,10 @@
         <v>10.7273</v>
       </c>
       <c r="D31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7601</v>
+        <v>2.3703</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.4545</v>
+        <v>12.7273</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>3.4457</v>
+        <v>3.5239</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>6.2512</v>
+        <v>7.1227</v>
       </c>
       <c r="D33" t="n">
-        <v>6.2404</v>
+        <v>7.0394</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4247</v>
+        <v>0.4395</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1336,7 +1336,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34205</v>
+        <v>36044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03344539</v>
+        <v>0.03524355</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>701</v>
+        <v>804</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00068543</v>
+        <v>0.00078615</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>114.7819</v>
+        <v>132.5147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1553,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03785717</v>
+        <v>0.03988112</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.034249</v>
+        <v>0.03614952</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1613,6 +1613,86 @@
         </is>
       </c>
       <c r="D14" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>unattached_length_px</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>px</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>unattached_component_count</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>30</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>canalicular_length_density_attached_per_px</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>0.03524355</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>field_length_density_with_unattached_per_px</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>0.03579111</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
         </is>
@@ -1666,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6.9427</v>
+        <v>7.7083</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1686,7 +1766,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>7.2111</v>
+        <v>8</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1726,7 +1806,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>10.198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1746,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>32870</v>
+        <v>34694</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1889,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>539</v>
+        <v>589</v>
       </c>
     </row>
     <row r="9">
@@ -1904,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.2955</v>
+        <v>21.9286</v>
       </c>
     </row>
     <row r="10">
@@ -1934,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>46.9235</v>
+        <v>45.2261</v>
       </c>
     </row>
     <row r="12">
@@ -1949,7 +2029,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0471</v>
+        <v>50.0379</v>
       </c>
     </row>
     <row r="13">
@@ -1964,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.423</v>
+        <v>0.4244</v>
       </c>
     </row>
     <row r="14">
@@ -1979,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.577</v>
+        <v>0.5756</v>
       </c>
     </row>
     <row r="15">
@@ -2056,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
@@ -2071,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="21">
@@ -2135,7 +2215,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9374</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="25">
@@ -2165,7 +2245,7 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1.3</v>
+        <v>1.3257</v>
       </c>
     </row>
   </sheetData>
@@ -2384,22 +2464,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M2" t="n">
         <v>96</v>
       </c>
       <c r="N2" t="n">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="O2" t="n">
-        <v>2226.1778</v>
+        <v>3081.4936</v>
       </c>
       <c r="P2" t="n">
-        <v>107</v>
+        <v>141</v>
       </c>
       <c r="Q2" t="n">
-        <v>20.8054</v>
+        <v>21.8546</v>
       </c>
       <c r="R2" t="n">
         <v>105.1543</v>
@@ -2420,22 +2500,22 @@
         <v>0.02593894</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02184824</v>
+        <v>0.02165141</v>
       </c>
       <c r="Y2" t="n">
-        <v>2.8529</v>
+        <v>1.902</v>
       </c>
       <c r="Z2" t="n">
         <v>81</v>
       </c>
       <c r="AA2" t="n">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="AB2" t="n">
         <v>103.4264</v>
       </c>
       <c r="AC2" t="n">
-        <v>244.2376</v>
+        <v>241.8234</v>
       </c>
       <c r="AD2" t="n">
         <v>3</v>
@@ -2482,7 +2562,7 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M3" t="n">
         <v>42</v>
@@ -2521,7 +2601,7 @@
         <v>0.01183971</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.5055</v>
+        <v>2.2582</v>
       </c>
       <c r="Z3" t="n">
         <v>38</v>
@@ -2583,19 +2663,19 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="N4" t="n">
-        <v>736</v>
+        <v>752</v>
       </c>
       <c r="O4" t="n">
-        <v>1052.6955</v>
+        <v>1973.2662</v>
       </c>
       <c r="P4" t="n">
-        <v>46</v>
+        <v>97</v>
       </c>
       <c r="Q4" t="n">
-        <v>22.8847</v>
+        <v>20.343</v>
       </c>
       <c r="R4" t="n">
         <v>219.6812</v>
@@ -2613,25 +2693,25 @@
         <v>0.9689</v>
       </c>
       <c r="W4" t="n">
-        <v>0.03631907</v>
+        <v>0.0366533</v>
       </c>
       <c r="X4" t="n">
-        <v>0.03552981</v>
+        <v>0.0363022</v>
       </c>
       <c r="Y4" t="n">
         <v>3.6416</v>
       </c>
       <c r="Z4" t="n">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AA4" t="n">
-        <v>446</v>
+        <v>462</v>
       </c>
       <c r="AB4" t="n">
-        <v>363.0782</v>
+        <v>366.9066</v>
       </c>
       <c r="AC4" t="n">
-        <v>813.4701</v>
+        <v>831.9554000000001</v>
       </c>
       <c r="AD4" t="n">
         <v>7</v>
@@ -2640,10 +2720,10 @@
         <v>12</v>
       </c>
       <c r="AF4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.7931</v>
+        <v>6.7412</v>
       </c>
     </row>
     <row r="5">
@@ -2681,22 +2761,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M5" t="n">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="N5" t="n">
-        <v>824</v>
+        <v>1001</v>
       </c>
       <c r="O5" t="n">
-        <v>2781.3191</v>
+        <v>4443.2127</v>
       </c>
       <c r="P5" t="n">
-        <v>135</v>
+        <v>216</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.6024</v>
+        <v>20.5704</v>
       </c>
       <c r="R5" t="n">
         <v>210.2437</v>
@@ -2714,37 +2794,37 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.03924333</v>
+        <v>0.04406063</v>
       </c>
       <c r="X5" t="n">
-        <v>0.0364747</v>
+        <v>0.04430968</v>
       </c>
       <c r="Y5" t="n">
-        <v>2.8538</v>
+        <v>4.7564</v>
       </c>
       <c r="Z5" t="n">
-        <v>284</v>
+        <v>323</v>
       </c>
       <c r="AA5" t="n">
-        <v>624</v>
+        <v>779</v>
       </c>
       <c r="AB5" t="n">
-        <v>381.1198</v>
+        <v>430.7473</v>
       </c>
       <c r="AC5" t="n">
-        <v>948.0925</v>
+        <v>1149.46</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AE5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF5" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>5.8974</v>
+        <v>6.9373</v>
       </c>
     </row>
     <row r="6">
@@ -2782,22 +2862,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="N6" t="n">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="O6" t="n">
-        <v>2586.3931</v>
+        <v>3405.8927</v>
       </c>
       <c r="P6" t="n">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="Q6" t="n">
-        <v>22.1059</v>
+        <v>20.7676</v>
       </c>
       <c r="R6" t="n">
         <v>335.4214</v>
@@ -2815,37 +2895,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02824766</v>
+        <v>0.02742651</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03026861</v>
+        <v>0.03020179</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.6832</v>
+        <v>1.4907</v>
       </c>
       <c r="Z6" t="n">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="AA6" t="n">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="AB6" t="n">
-        <v>386.1198</v>
+        <v>372.0782</v>
       </c>
       <c r="AC6" t="n">
-        <v>1011.6367</v>
+        <v>1001.7666</v>
       </c>
       <c r="AD6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>11</v>
+      </c>
+      <c r="AF6" t="n">
         <v>9</v>
       </c>
-      <c r="AE6" t="n">
-        <v>12</v>
-      </c>
-      <c r="AF6" t="n">
-        <v>12</v>
-      </c>
       <c r="AG6" t="n">
-        <v>6.5577</v>
+        <v>7.2307</v>
       </c>
     </row>
     <row r="7">
@@ -2883,22 +2963,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M7" t="n">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="N7" t="n">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="O7" t="n">
-        <v>1286.9575</v>
+        <v>1275.6438</v>
       </c>
       <c r="P7" t="n">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="Q7" t="n">
-        <v>18.1262</v>
+        <v>21.2607</v>
       </c>
       <c r="R7" t="n">
         <v>167.2376</v>
@@ -2916,25 +2996,25 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02712091</v>
+        <v>0.02752171</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03308716</v>
+        <v>0.03328151</v>
       </c>
       <c r="Y7" t="n">
-        <v>2.9898</v>
+        <v>1.7939</v>
       </c>
       <c r="Z7" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="AA7" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AB7" t="n">
-        <v>227.4092</v>
+        <v>236.1371</v>
       </c>
       <c r="AC7" t="n">
-        <v>782.2102</v>
+        <v>787.6245</v>
       </c>
       <c r="AD7" t="n">
         <v>6</v>
@@ -2943,10 +3023,10 @@
         <v>7</v>
       </c>
       <c r="AF7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>6.8732</v>
+        <v>7.8564</v>
       </c>
     </row>
     <row r="8">
@@ -2984,22 +3064,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M8" t="n">
-        <v>325</v>
+        <v>352</v>
       </c>
       <c r="N8" t="n">
-        <v>804</v>
+        <v>883</v>
       </c>
       <c r="O8" t="n">
-        <v>4019.5811</v>
+        <v>4044.5395</v>
       </c>
       <c r="P8" t="n">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.4951</v>
+        <v>21.1756</v>
       </c>
       <c r="R8" t="n">
         <v>243.5219</v>
@@ -3017,37 +3097,37 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03431166</v>
+        <v>0.03716216</v>
       </c>
       <c r="X8" t="n">
-        <v>0.03645267</v>
+        <v>0.04003446</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.2851</v>
+        <v>2.4638</v>
       </c>
       <c r="Z8" t="n">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="AA8" t="n">
-        <v>505</v>
+        <v>591</v>
       </c>
       <c r="AB8" t="n">
-        <v>354.4508</v>
+        <v>392.9066</v>
       </c>
       <c r="AC8" t="n">
-        <v>900.1392</v>
+        <v>994.3229</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE8" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>6.1013</v>
+        <v>7.3054</v>
       </c>
     </row>
     <row r="9">
@@ -3085,22 +3165,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M9" t="n">
-        <v>427</v>
+        <v>463</v>
       </c>
       <c r="N9" t="n">
-        <v>909</v>
+        <v>976</v>
       </c>
       <c r="O9" t="n">
-        <v>2843.4592</v>
+        <v>3223.2947</v>
       </c>
       <c r="P9" t="n">
-        <v>118</v>
+        <v>144</v>
       </c>
       <c r="Q9" t="n">
-        <v>24.0971</v>
+        <v>22.384</v>
       </c>
       <c r="R9" t="n">
         <v>167.9239</v>
@@ -3118,37 +3198,37 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.05810314</v>
+        <v>0.06300177</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05178012</v>
+        <v>0.0555967</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.3596</v>
+        <v>4.1686</v>
       </c>
       <c r="Z9" t="n">
-        <v>404</v>
+        <v>451</v>
       </c>
       <c r="AA9" t="n">
-        <v>806</v>
+        <v>949</v>
       </c>
       <c r="AB9" t="n">
-        <v>479.6051</v>
+        <v>523.5757</v>
       </c>
       <c r="AC9" t="n">
-        <v>1014.3818</v>
+        <v>1094.4945</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>6.4156</v>
+        <v>7.4331</v>
       </c>
     </row>
     <row r="10">
@@ -3186,22 +3266,22 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="M10" t="n">
-        <v>230</v>
+        <v>299</v>
       </c>
       <c r="N10" t="n">
-        <v>651</v>
+        <v>760</v>
       </c>
       <c r="O10" t="n">
-        <v>1554.8448</v>
+        <v>711.6173</v>
       </c>
       <c r="P10" t="n">
-        <v>73</v>
+        <v>30</v>
       </c>
       <c r="Q10" t="n">
-        <v>21.2992</v>
+        <v>23.7206</v>
       </c>
       <c r="R10" t="n">
         <v>282.8944</v>
@@ -3219,37 +3299,37 @@
         <v>0.7462</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0265038</v>
+        <v>0.03445494</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03367474</v>
+        <v>0.03931306</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.1209</v>
+        <v>2.8279</v>
       </c>
       <c r="Z10" t="n">
-        <v>144</v>
+        <v>180</v>
       </c>
       <c r="AA10" t="n">
-        <v>336</v>
+        <v>495</v>
       </c>
       <c r="AB10" t="n">
-        <v>251.5097</v>
+        <v>336.2498</v>
       </c>
       <c r="AC10" t="n">
-        <v>728.1858999999999</v>
+        <v>850.8549</v>
       </c>
       <c r="AD10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>6.6498</v>
+        <v>7.398</v>
       </c>
     </row>
     <row r="11">
@@ -3287,22 +3367,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M11" t="n">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="N11" t="n">
-        <v>1099</v>
+        <v>1143</v>
       </c>
       <c r="O11" t="n">
-        <v>1539.455</v>
+        <v>1597.8692</v>
       </c>
       <c r="P11" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="Q11" t="n">
-        <v>26.0925</v>
+        <v>24.5826</v>
       </c>
       <c r="R11" t="n">
         <v>263.4802</v>
@@ -3320,37 +3400,37 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03293354</v>
+        <v>0.03440818</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04476214</v>
+        <v>0.04655425</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5181</v>
+        <v>1.8977</v>
       </c>
       <c r="Z11" t="n">
-        <v>221</v>
+        <v>248</v>
       </c>
       <c r="AA11" t="n">
-        <v>658</v>
+        <v>848</v>
       </c>
       <c r="AB11" t="n">
-        <v>377.664</v>
+        <v>392.9066</v>
       </c>
       <c r="AC11" t="n">
-        <v>1230.1341</v>
+        <v>1281.3473</v>
       </c>
       <c r="AD11" t="n">
         <v>6</v>
       </c>
       <c r="AE11" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AF11" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>6.5434</v>
+        <v>7.7674</v>
       </c>
     </row>
     <row r="12">
@@ -3388,22 +3468,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M12" t="n">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="N12" t="n">
-        <v>613</v>
+        <v>629</v>
       </c>
       <c r="O12" t="n">
-        <v>360.1493</v>
+        <v>362.463</v>
       </c>
       <c r="P12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>24.01</v>
+        <v>27.8818</v>
       </c>
       <c r="R12" t="n">
         <v>174.5097</v>
@@ -3421,28 +3501,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.02906209</v>
+        <v>0.03077939</v>
       </c>
       <c r="X12" t="n">
-        <v>0.02951372</v>
+        <v>0.03028406</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.2921</v>
+        <v>2.8652</v>
       </c>
       <c r="Z12" t="n">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="AA12" t="n">
-        <v>207</v>
+        <v>293</v>
       </c>
       <c r="AB12" t="n">
-        <v>247.4802</v>
+        <v>264.3797</v>
       </c>
       <c r="AC12" t="n">
-        <v>707.4113</v>
+        <v>728.1392</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AE12" t="n">
         <v>10</v>
@@ -3451,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>5.8424</v>
+        <v>6.5248</v>
       </c>
     </row>
     <row r="13">
@@ -3492,19 +3572,19 @@
         <v>6</v>
       </c>
       <c r="M13" t="n">
-        <v>285</v>
+        <v>305</v>
       </c>
       <c r="N13" t="n">
-        <v>835</v>
+        <v>862</v>
       </c>
       <c r="O13" t="n">
-        <v>1173.8032</v>
+        <v>1346.9869</v>
       </c>
       <c r="P13" t="n">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="Q13" t="n">
-        <v>24.4542</v>
+        <v>20.1043</v>
       </c>
       <c r="R13" t="n">
         <v>210.1665</v>
@@ -3522,37 +3602,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03296322</v>
+        <v>0.03527643</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03763126</v>
+        <v>0.03884808</v>
       </c>
       <c r="Y13" t="n">
         <v>2.8549</v>
       </c>
       <c r="Z13" t="n">
-        <v>220</v>
+        <v>249</v>
       </c>
       <c r="AA13" t="n">
-        <v>547</v>
+        <v>610</v>
       </c>
       <c r="AB13" t="n">
-        <v>330.1909</v>
+        <v>353.0193</v>
       </c>
       <c r="AC13" t="n">
-        <v>946.8792999999999</v>
+        <v>973.2224</v>
       </c>
       <c r="AD13" t="n">
         <v>7</v>
       </c>
       <c r="AE13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AF13" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>5.5278</v>
+        <v>6.8676</v>
       </c>
     </row>
     <row r="14">
@@ -3590,22 +3670,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M14" t="n">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="N14" t="n">
-        <v>686</v>
+        <v>700</v>
       </c>
       <c r="O14" t="n">
-        <v>903.7077</v>
+        <v>610.529</v>
       </c>
       <c r="P14" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="Q14" t="n">
-        <v>23.7818</v>
+        <v>24.4212</v>
       </c>
       <c r="R14" t="n">
         <v>185.8234</v>
@@ -3623,25 +3703,25 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02218045</v>
+        <v>0.02180451</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03174456</v>
+        <v>0.03239241</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.6907</v>
+        <v>1.6144</v>
       </c>
       <c r="Z14" t="n">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AA14" t="n">
-        <v>376</v>
+        <v>390</v>
       </c>
       <c r="AB14" t="n">
-        <v>201.1665</v>
+        <v>199.1665</v>
       </c>
       <c r="AC14" t="n">
-        <v>786.6955</v>
+        <v>799.4529</v>
       </c>
       <c r="AD14" t="n">
         <v>5</v>
@@ -3653,7 +3733,7 @@
         <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>6.2404</v>
+        <v>7.0394</v>
       </c>
     </row>
     <row r="15">
@@ -3691,22 +3771,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="M15" t="n">
-        <v>325</v>
+        <v>346</v>
       </c>
       <c r="N15" t="n">
-        <v>918</v>
+        <v>971</v>
       </c>
       <c r="O15" t="n">
-        <v>889.8377</v>
+        <v>557.9605</v>
       </c>
       <c r="P15" t="n">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="Q15" t="n">
-        <v>24.0497</v>
+        <v>19.24</v>
       </c>
       <c r="R15" t="n">
         <v>259.2792</v>
@@ -3724,25 +3804,25 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03361258</v>
+        <v>0.03578447</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03697885</v>
+        <v>0.0391138</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.4712</v>
+        <v>2.6998</v>
       </c>
       <c r="Z15" t="n">
-        <v>304</v>
+        <v>325</v>
       </c>
       <c r="AA15" t="n">
-        <v>615</v>
+        <v>727</v>
       </c>
       <c r="AB15" t="n">
-        <v>363.664</v>
+        <v>387.3209</v>
       </c>
       <c r="AC15" t="n">
-        <v>1032.0214</v>
+        <v>1091.2641</v>
       </c>
       <c r="AD15" t="n">
         <v>10</v>
@@ -3754,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>5.9713</v>
+        <v>6.646</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z23/5_quantification/682_z23_quantification.xlsx
+++ b/results/682_z23/5_quantification/682_z23_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5.9091</v>
+        <v>7.4545</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0715</v>
+        <v>2.4234</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>315.1818</v>
+        <v>315.8182</v>
       </c>
       <c r="D13" t="n">
         <v>334</v>
       </c>
       <c r="E13" t="n">
-        <v>82.5843</v>
+        <v>82.349</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>864.1818</v>
+        <v>865.0909</v>
       </c>
       <c r="D14" t="n">
         <v>883</v>
       </c>
       <c r="E14" t="n">
-        <v>157.884</v>
+        <v>157.4868</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2076.5144</v>
+        <v>2069.9248</v>
       </c>
       <c r="D15" t="n">
-        <v>1597.8692</v>
+        <v>1463.7565</v>
       </c>
       <c r="E15" t="n">
-        <v>1461.6153</v>
+        <v>1374.1261</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>97.36360000000001</v>
+        <v>96.36360000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E16" t="n">
-        <v>70.6049</v>
+        <v>67.4867</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.0665</v>
+        <v>22.5291</v>
       </c>
       <c r="D17" t="n">
-        <v>21.1756</v>
+        <v>21.5522</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5685</v>
+        <v>2.3922</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03580719</v>
+        <v>0.03588123</v>
       </c>
       <c r="D23" t="n">
         <v>0.03527643</v>
       </c>
       <c r="E23" t="n">
-        <v>0.0108291</v>
+        <v>0.01079956</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03881081</v>
+        <v>0.03885196</v>
       </c>
       <c r="D24" t="n">
         <v>0.03884808</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00773588</v>
+        <v>0.00771624</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.7497</v>
+        <v>3.4794</v>
       </c>
       <c r="D25" t="n">
-        <v>2.6998</v>
+        <v>3.5877</v>
       </c>
       <c r="E25" t="n">
-        <v>1.0704</v>
+        <v>1.3278</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>256.9091</v>
+        <v>257.5455</v>
       </c>
       <c r="D26" t="n">
         <v>249</v>
       </c>
       <c r="E26" t="n">
-        <v>94.1652</v>
+        <v>94.1758</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>596.4545000000001</v>
+        <v>597.3636</v>
       </c>
       <c r="D27" t="n">
         <v>591</v>
       </c>
       <c r="E27" t="n">
-        <v>215.5701</v>
+        <v>215.0662</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>356.2859</v>
+        <v>356.9975</v>
       </c>
       <c r="D28" t="n">
         <v>372.0782</v>
       </c>
       <c r="E28" t="n">
-        <v>92.25920000000001</v>
+        <v>91.9081</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>975.7318</v>
+        <v>976.7915</v>
       </c>
       <c r="D29" t="n">
         <v>994.3229</v>
       </c>
       <c r="E29" t="n">
-        <v>173.3484</v>
+        <v>172.8732</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.1227</v>
+        <v>7.1595</v>
       </c>
       <c r="D33" t="n">
         <v>7.0394</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4395</v>
+        <v>0.4535</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36044</v>
+        <v>36058</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03524355</v>
+        <v>0.03525724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>132.5147</v>
+        <v>133.0554</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03988112</v>
+        <v>0.03989781</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03614952</v>
+        <v>0.03616411</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03524355</v>
+        <v>0.03525724</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03579111</v>
+        <v>0.0358048</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7083</v>
+        <v>7.7188</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34694</v>
+        <v>34708</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>589</v>
+        <v>591</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.9286</v>
+        <v>21.8209</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.2261</v>
+        <v>45.1778</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4244</v>
+        <v>0.423</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5756</v>
+        <v>0.577</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="21">
@@ -2761,7 +2761,7 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M5" t="n">
         <v>375</v>
@@ -2800,7 +2800,7 @@
         <v>0.04430968</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.7564</v>
+        <v>5.232</v>
       </c>
       <c r="Z5" t="n">
         <v>323</v>
@@ -2862,7 +2862,7 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M6" t="n">
         <v>334</v>
@@ -2871,13 +2871,13 @@
         <v>904</v>
       </c>
       <c r="O6" t="n">
-        <v>3405.8927</v>
+        <v>3085.7556</v>
       </c>
       <c r="P6" t="n">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.7676</v>
+        <v>20.4355</v>
       </c>
       <c r="R6" t="n">
         <v>335.4214</v>
@@ -2901,7 +2901,7 @@
         <v>0.03020179</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.4907</v>
+        <v>2.0869</v>
       </c>
       <c r="Z6" t="n">
         <v>307</v>
@@ -2963,22 +2963,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="N7" t="n">
-        <v>685</v>
+        <v>691</v>
       </c>
       <c r="O7" t="n">
-        <v>1275.6438</v>
+        <v>1314.6854</v>
       </c>
       <c r="P7" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.2607</v>
+        <v>21.5522</v>
       </c>
       <c r="R7" t="n">
         <v>167.2376</v>
@@ -2996,25 +2996,25 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02752171</v>
+        <v>0.02792251</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03328151</v>
+        <v>0.03357302</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.7939</v>
+        <v>3.5877</v>
       </c>
       <c r="Z7" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AA7" t="n">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="AB7" t="n">
-        <v>236.1371</v>
+        <v>239.9655</v>
       </c>
       <c r="AC7" t="n">
-        <v>787.6245</v>
+        <v>794.8671000000001</v>
       </c>
       <c r="AD7" t="n">
         <v>6</v>
@@ -3026,7 +3026,7 @@
         <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>7.8564</v>
+        <v>8.039199999999999</v>
       </c>
     </row>
     <row r="8">
@@ -3064,7 +3064,7 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M8" t="n">
         <v>352</v>
@@ -3073,13 +3073,13 @@
         <v>883</v>
       </c>
       <c r="O8" t="n">
-        <v>4044.5395</v>
+        <v>3884.7283</v>
       </c>
       <c r="P8" t="n">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.1756</v>
+        <v>21.3447</v>
       </c>
       <c r="R8" t="n">
         <v>243.5219</v>
@@ -3103,7 +3103,7 @@
         <v>0.04003446</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.4638</v>
+        <v>2.8745</v>
       </c>
       <c r="Z8" t="n">
         <v>281</v>
@@ -3165,7 +3165,7 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
         <v>463</v>
@@ -3174,13 +3174,13 @@
         <v>976</v>
       </c>
       <c r="O9" t="n">
-        <v>3223.2947</v>
+        <v>3247.6084</v>
       </c>
       <c r="P9" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.384</v>
+        <v>22.0926</v>
       </c>
       <c r="R9" t="n">
         <v>167.9239</v>
@@ -3204,7 +3204,7 @@
         <v>0.0555967</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.1686</v>
+        <v>5.9551</v>
       </c>
       <c r="Z9" t="n">
         <v>451</v>
@@ -3266,7 +3266,7 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="M10" t="n">
         <v>299</v>
@@ -3275,13 +3275,13 @@
         <v>760</v>
       </c>
       <c r="O10" t="n">
-        <v>711.6173</v>
+        <v>1191.394</v>
       </c>
       <c r="P10" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.7206</v>
+        <v>23.8279</v>
       </c>
       <c r="R10" t="n">
         <v>282.8944</v>
@@ -3305,7 +3305,7 @@
         <v>0.03931306</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.8279</v>
+        <v>3.8884</v>
       </c>
       <c r="Z10" t="n">
         <v>180</v>
@@ -3367,7 +3367,7 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M11" t="n">
         <v>350</v>
@@ -3376,13 +3376,13 @@
         <v>1143</v>
       </c>
       <c r="O11" t="n">
-        <v>1597.8692</v>
+        <v>1463.7565</v>
       </c>
       <c r="P11" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q11" t="n">
-        <v>24.5826</v>
+        <v>22.8712</v>
       </c>
       <c r="R11" t="n">
         <v>263.4802</v>
@@ -3406,7 +3406,7 @@
         <v>0.04655425</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.8977</v>
+        <v>2.2772</v>
       </c>
       <c r="Z11" t="n">
         <v>248</v>
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M13" t="n">
         <v>305</v>
@@ -3578,13 +3578,13 @@
         <v>862</v>
       </c>
       <c r="O13" t="n">
-        <v>1346.9869</v>
+        <v>1222.9747</v>
       </c>
       <c r="P13" t="n">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="Q13" t="n">
-        <v>20.1043</v>
+        <v>21.0858</v>
       </c>
       <c r="R13" t="n">
         <v>210.1665</v>
@@ -3608,7 +3608,7 @@
         <v>0.03884808</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.8549</v>
+        <v>4.2823</v>
       </c>
       <c r="Z13" t="n">
         <v>249</v>
@@ -3771,22 +3771,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M15" t="n">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="N15" t="n">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="O15" t="n">
-        <v>557.9605</v>
+        <v>1160.193</v>
       </c>
       <c r="P15" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="Q15" t="n">
-        <v>19.24</v>
+        <v>25.2216</v>
       </c>
       <c r="R15" t="n">
         <v>259.2792</v>
@@ -3804,25 +3804,25 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03578447</v>
+        <v>0.03619816</v>
       </c>
       <c r="X15" t="n">
-        <v>0.0391138</v>
+        <v>0.03927492</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.6998</v>
+        <v>3.8568</v>
       </c>
       <c r="Z15" t="n">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="AA15" t="n">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="AB15" t="n">
-        <v>387.3209</v>
+        <v>391.3209</v>
       </c>
       <c r="AC15" t="n">
-        <v>1091.2641</v>
+        <v>1095.6783</v>
       </c>
       <c r="AD15" t="n">
         <v>10</v>
@@ -3834,7 +3834,7 @@
         <v>14</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.646</v>
+        <v>6.8683</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z23/5_quantification/682_z23_quantification.xlsx
+++ b/results/682_z23/5_quantification/682_z23_quantification.xlsx
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>7.4545</v>
+        <v>8.6364</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4234</v>
+        <v>2.6181</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>315.8182</v>
+        <v>348.3636</v>
       </c>
       <c r="D13" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="E13" t="n">
-        <v>82.349</v>
+        <v>87.1324</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>865.0909</v>
+        <v>900.9091</v>
       </c>
       <c r="D14" t="n">
-        <v>883</v>
+        <v>900</v>
       </c>
       <c r="E14" t="n">
-        <v>157.4868</v>
+        <v>167.6451</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2069.9248</v>
+        <v>2403.5318</v>
       </c>
       <c r="D15" t="n">
-        <v>1463.7565</v>
+        <v>1927.3667</v>
       </c>
       <c r="E15" t="n">
-        <v>1374.1261</v>
+        <v>1454.4606</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>96.36360000000001</v>
+        <v>112</v>
       </c>
       <c r="D16" t="n">
-        <v>64</v>
+        <v>96</v>
       </c>
       <c r="E16" t="n">
-        <v>67.4867</v>
+        <v>71.8999</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.5291</v>
+        <v>22.1506</v>
       </c>
       <c r="D17" t="n">
-        <v>21.5522</v>
+        <v>21.3106</v>
       </c>
       <c r="E17" t="n">
-        <v>2.3922</v>
+        <v>3.1481</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03588123</v>
+        <v>0.03965443</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03527643</v>
+        <v>0.03724266</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01079956</v>
+        <v>0.01151573</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.03885196</v>
+        <v>0.0404533</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03884808</v>
+        <v>0.03961422</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00771624</v>
+        <v>0.00805999</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3.4794</v>
+        <v>4.0142</v>
       </c>
       <c r="D25" t="n">
-        <v>3.5877</v>
+        <v>3.6416</v>
       </c>
       <c r="E25" t="n">
-        <v>1.3278</v>
+        <v>1.4325</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>257.5455</v>
+        <v>302.2727</v>
       </c>
       <c r="D26" t="n">
-        <v>249</v>
+        <v>292</v>
       </c>
       <c r="E26" t="n">
-        <v>94.1758</v>
+        <v>101.1702</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>597.3636</v>
+        <v>674.4545000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>591</v>
+        <v>605</v>
       </c>
       <c r="E27" t="n">
-        <v>215.0662</v>
+        <v>230.6085</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>356.9975</v>
+        <v>393.8255</v>
       </c>
       <c r="D28" t="n">
-        <v>372.0782</v>
+        <v>392.7351</v>
       </c>
       <c r="E28" t="n">
-        <v>91.9081</v>
+        <v>98.2953</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>976.7915</v>
+        <v>1017.4285</v>
       </c>
       <c r="D29" t="n">
-        <v>994.3229</v>
+        <v>1012.5656</v>
       </c>
       <c r="E29" t="n">
-        <v>172.8732</v>
+        <v>185.5464</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>7.5455</v>
+        <v>8.3636</v>
       </c>
       <c r="D30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>2.2523</v>
+        <v>1.9633</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>10.7273</v>
+        <v>11.0909</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.3703</v>
+        <v>2.7002</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.7273</v>
+        <v>12.8182</v>
       </c>
       <c r="D32" t="n">
         <v>12</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5239</v>
+        <v>3.5726</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>7.1595</v>
+        <v>7.1663</v>
       </c>
       <c r="D33" t="n">
-        <v>7.0394</v>
+        <v>7.2028</v>
       </c>
       <c r="E33" t="n">
-        <v>0.4535</v>
+        <v>0.3366</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1393,7 +1393,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36058</v>
+        <v>38363</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1413,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03525724</v>
+        <v>0.03751105</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>804</v>
+        <v>880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00078615</v>
+        <v>0.00086046</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>133.0554</v>
+        <v>145.8669</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.03989781</v>
+        <v>0.0424887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1593,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03616411</v>
+        <v>0.03854185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03525724</v>
+        <v>0.03751105</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,7 +1690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.0358048</v>
+        <v>0.03805861</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1746,7 +1746,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7188</v>
+        <v>7.7464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>4</v>
+        <v>4.4721</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1826,7 +1826,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34708</v>
+        <v>36990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>591</v>
+        <v>652</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +1984,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.8209</v>
+        <v>21.2147</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>45.1778</v>
+        <v>44.4822</v>
       </c>
     </row>
     <row r="12">
@@ -2044,7 +2044,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.423</v>
+        <v>0.4095</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2059,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.577</v>
+        <v>0.5905</v>
       </c>
     </row>
     <row r="15">
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19">
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2151,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="21">
@@ -2230,7 +2230,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.52</v>
+        <v>0.5814</v>
       </c>
     </row>
     <row r="26">
@@ -2473,13 +2473,13 @@
         <v>220</v>
       </c>
       <c r="O2" t="n">
-        <v>3081.4936</v>
+        <v>3079.4936</v>
       </c>
       <c r="P2" t="n">
         <v>141</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.8546</v>
+        <v>21.8404</v>
       </c>
       <c r="R2" t="n">
         <v>105.1543</v>
@@ -2669,13 +2669,13 @@
         <v>752</v>
       </c>
       <c r="O4" t="n">
-        <v>1973.2662</v>
+        <v>1927.3667</v>
       </c>
       <c r="P4" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.343</v>
+        <v>20.0767</v>
       </c>
       <c r="R4" t="n">
         <v>219.6812</v>
@@ -2761,22 +2761,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M5" t="n">
-        <v>375</v>
+        <v>461</v>
       </c>
       <c r="N5" t="n">
-        <v>1001</v>
+        <v>1086</v>
       </c>
       <c r="O5" t="n">
-        <v>4443.2127</v>
+        <v>5431.624</v>
       </c>
       <c r="P5" t="n">
-        <v>216</v>
+        <v>268</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.5704</v>
+        <v>20.2673</v>
       </c>
       <c r="R5" t="n">
         <v>210.2437</v>
@@ -2794,37 +2794,37 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.04406063</v>
+        <v>0.0541652</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04430968</v>
+        <v>0.04807224</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.232</v>
+        <v>5.7077</v>
       </c>
       <c r="Z5" t="n">
-        <v>323</v>
+        <v>450</v>
       </c>
       <c r="AA5" t="n">
-        <v>779</v>
+        <v>1055</v>
       </c>
       <c r="AB5" t="n">
-        <v>430.7473</v>
+        <v>531.5168</v>
       </c>
       <c r="AC5" t="n">
-        <v>1149.46</v>
+        <v>1247.1585</v>
       </c>
       <c r="AD5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AF5" t="n">
         <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>6.9373</v>
+        <v>7.2028</v>
       </c>
     </row>
     <row r="6">
@@ -2862,22 +2862,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="M6" t="n">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="N6" t="n">
-        <v>904</v>
+        <v>922</v>
       </c>
       <c r="O6" t="n">
-        <v>3085.7556</v>
+        <v>3128.1698</v>
       </c>
       <c r="P6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.4355</v>
+        <v>20.0524</v>
       </c>
       <c r="R6" t="n">
         <v>335.4214</v>
@@ -2895,37 +2895,37 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02742651</v>
+        <v>0.02890458</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03020179</v>
+        <v>0.03080315</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.0869</v>
+        <v>2.6832</v>
       </c>
       <c r="Z6" t="n">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="AA6" t="n">
-        <v>587</v>
+        <v>605</v>
       </c>
       <c r="AB6" t="n">
-        <v>372.0782</v>
+        <v>392.7351</v>
       </c>
       <c r="AC6" t="n">
-        <v>1001.7666</v>
+        <v>1022.4234</v>
       </c>
       <c r="AD6" t="n">
         <v>8</v>
       </c>
       <c r="AE6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF6" t="n">
         <v>9</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.2307</v>
+        <v>7.4414</v>
       </c>
     </row>
     <row r="7">
@@ -2963,22 +2963,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M7" t="n">
-        <v>209</v>
+        <v>261</v>
       </c>
       <c r="N7" t="n">
-        <v>691</v>
+        <v>743</v>
       </c>
       <c r="O7" t="n">
-        <v>1314.6854</v>
+        <v>1344.8276</v>
       </c>
       <c r="P7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.5522</v>
+        <v>21.6908</v>
       </c>
       <c r="R7" t="n">
         <v>167.2376</v>
@@ -2996,37 +2996,37 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.02792251</v>
+        <v>0.03486974</v>
       </c>
       <c r="X7" t="n">
-        <v>0.03357302</v>
+        <v>0.0360995</v>
       </c>
       <c r="Y7" t="n">
-        <v>3.5877</v>
+        <v>4.1857</v>
       </c>
       <c r="Z7" t="n">
-        <v>169</v>
+        <v>224</v>
       </c>
       <c r="AA7" t="n">
-        <v>331</v>
+        <v>403</v>
       </c>
       <c r="AB7" t="n">
-        <v>239.9655</v>
+        <v>301.8356</v>
       </c>
       <c r="AC7" t="n">
-        <v>794.8671000000001</v>
+        <v>856.7372</v>
       </c>
       <c r="AD7" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE7" t="n">
         <v>6</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>7</v>
       </c>
       <c r="AF7" t="n">
         <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>8.039199999999999</v>
+        <v>7.6091</v>
       </c>
     </row>
     <row r="8">
@@ -3067,19 +3067,19 @@
         <v>7</v>
       </c>
       <c r="M8" t="n">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="N8" t="n">
-        <v>883</v>
+        <v>900</v>
       </c>
       <c r="O8" t="n">
-        <v>3884.7283</v>
+        <v>3942.4562</v>
       </c>
       <c r="P8" t="n">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.3447</v>
+        <v>21.3106</v>
       </c>
       <c r="R8" t="n">
         <v>243.5219</v>
@@ -3097,25 +3097,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03716216</v>
+        <v>0.03895693</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04003446</v>
+        <v>0.04080522</v>
       </c>
       <c r="Y8" t="n">
         <v>2.8745</v>
       </c>
       <c r="Z8" t="n">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="AA8" t="n">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="AB8" t="n">
-        <v>392.9066</v>
+        <v>411.1493</v>
       </c>
       <c r="AC8" t="n">
-        <v>994.3229</v>
+        <v>1012.5656</v>
       </c>
       <c r="AD8" t="n">
         <v>9</v>
@@ -3127,7 +3127,7 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.3054</v>
+        <v>7.2722</v>
       </c>
     </row>
     <row r="9">
@@ -3165,22 +3165,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M9" t="n">
-        <v>463</v>
+        <v>490</v>
       </c>
       <c r="N9" t="n">
-        <v>976</v>
+        <v>1003</v>
       </c>
       <c r="O9" t="n">
-        <v>3247.6084</v>
+        <v>2452.0256</v>
       </c>
       <c r="P9" t="n">
-        <v>147</v>
+        <v>116</v>
       </c>
       <c r="Q9" t="n">
-        <v>22.0926</v>
+        <v>21.1382</v>
       </c>
       <c r="R9" t="n">
         <v>167.9239</v>
@@ -3198,25 +3198,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06300177</v>
+        <v>0.06667574</v>
       </c>
       <c r="X9" t="n">
-        <v>0.0555967</v>
+        <v>0.05713472</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.9551</v>
+        <v>7.1461</v>
       </c>
       <c r="Z9" t="n">
-        <v>451</v>
+        <v>478</v>
       </c>
       <c r="AA9" t="n">
-        <v>949</v>
+        <v>976</v>
       </c>
       <c r="AB9" t="n">
-        <v>523.5757</v>
+        <v>552.8183</v>
       </c>
       <c r="AC9" t="n">
-        <v>1094.4945</v>
+        <v>1123.7372</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
@@ -3228,7 +3228,7 @@
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4331</v>
+        <v>7.4172</v>
       </c>
     </row>
     <row r="10">
@@ -3266,22 +3266,22 @@
         <v>1</v>
       </c>
       <c r="L10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>299</v>
+        <v>326</v>
       </c>
       <c r="N10" t="n">
-        <v>760</v>
+        <v>785</v>
       </c>
       <c r="O10" t="n">
-        <v>1191.394</v>
+        <v>1237.6072</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="Q10" t="n">
-        <v>23.8279</v>
+        <v>22.9187</v>
       </c>
       <c r="R10" t="n">
         <v>282.8944</v>
@@ -3299,28 +3299,28 @@
         <v>0.7462</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03445494</v>
+        <v>0.03756626</v>
       </c>
       <c r="X10" t="n">
-        <v>0.03931306</v>
+        <v>0.04060625</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.8884</v>
+        <v>3.5349</v>
       </c>
       <c r="Z10" t="n">
-        <v>180</v>
+        <v>271</v>
       </c>
       <c r="AA10" t="n">
-        <v>495</v>
+        <v>619</v>
       </c>
       <c r="AB10" t="n">
-        <v>336.2498</v>
+        <v>366.1493</v>
       </c>
       <c r="AC10" t="n">
-        <v>850.8549</v>
+        <v>879.1686</v>
       </c>
       <c r="AD10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
         <v>11</v>
@@ -3329,7 +3329,7 @@
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.398</v>
+        <v>7.5147</v>
       </c>
     </row>
     <row r="11">
@@ -3367,22 +3367,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M11" t="n">
-        <v>350</v>
+        <v>398</v>
       </c>
       <c r="N11" t="n">
-        <v>1143</v>
+        <v>1191</v>
       </c>
       <c r="O11" t="n">
-        <v>1463.7565</v>
+        <v>1534.3128</v>
       </c>
       <c r="P11" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.8712</v>
+        <v>22.9002</v>
       </c>
       <c r="R11" t="n">
         <v>263.4802</v>
@@ -3400,28 +3400,28 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03440818</v>
+        <v>0.03912702</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04655425</v>
+        <v>0.04850929</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.2772</v>
+        <v>3.4158</v>
       </c>
       <c r="Z11" t="n">
-        <v>248</v>
+        <v>345</v>
       </c>
       <c r="AA11" t="n">
-        <v>848</v>
+        <v>889</v>
       </c>
       <c r="AB11" t="n">
-        <v>392.9066</v>
+        <v>448.1198</v>
       </c>
       <c r="AC11" t="n">
-        <v>1281.3473</v>
+        <v>1336.5605</v>
       </c>
       <c r="AD11" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>13</v>
@@ -3430,7 +3430,7 @@
         <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.7674</v>
+        <v>7.5386</v>
       </c>
     </row>
     <row r="12">
@@ -3468,22 +3468,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="M12" t="n">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="N12" t="n">
-        <v>629</v>
+        <v>659</v>
       </c>
       <c r="O12" t="n">
-        <v>362.463</v>
+        <v>1140.4133</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="Q12" t="n">
-        <v>27.8818</v>
+        <v>30.822</v>
       </c>
       <c r="R12" t="n">
         <v>174.5097</v>
@@ -3501,28 +3501,28 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.03077939</v>
+        <v>0.032893</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03028406</v>
+        <v>0.03172845</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.8652</v>
+        <v>3.4382</v>
       </c>
       <c r="Z12" t="n">
-        <v>149</v>
+        <v>190</v>
       </c>
       <c r="AA12" t="n">
-        <v>293</v>
+        <v>412</v>
       </c>
       <c r="AB12" t="n">
-        <v>264.3797</v>
+        <v>282.865</v>
       </c>
       <c r="AC12" t="n">
-        <v>728.1392</v>
+        <v>763.6955</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AE12" t="n">
         <v>10</v>
@@ -3531,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.5248</v>
+        <v>6.6908</v>
       </c>
     </row>
     <row r="13">
@@ -3572,19 +3572,19 @@
         <v>9</v>
       </c>
       <c r="M13" t="n">
-        <v>305</v>
+        <v>322</v>
       </c>
       <c r="N13" t="n">
-        <v>862</v>
+        <v>879</v>
       </c>
       <c r="O13" t="n">
-        <v>1222.9747</v>
+        <v>1209.2174</v>
       </c>
       <c r="P13" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="Q13" t="n">
-        <v>21.0858</v>
+        <v>19.8232</v>
       </c>
       <c r="R13" t="n">
         <v>210.1665</v>
@@ -3602,37 +3602,37 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03527643</v>
+        <v>0.03724266</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03884808</v>
+        <v>0.03961422</v>
       </c>
       <c r="Y13" t="n">
         <v>4.2823</v>
       </c>
       <c r="Z13" t="n">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="AA13" t="n">
-        <v>610</v>
+        <v>623</v>
       </c>
       <c r="AB13" t="n">
-        <v>353.0193</v>
+        <v>370.8478</v>
       </c>
       <c r="AC13" t="n">
-        <v>973.2224</v>
+        <v>991.0509</v>
       </c>
       <c r="AD13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AF13" t="n">
         <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.8676</v>
+        <v>6.6855</v>
       </c>
     </row>
     <row r="14">
@@ -3670,22 +3670,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M14" t="n">
-        <v>174</v>
+        <v>208</v>
       </c>
       <c r="N14" t="n">
-        <v>700</v>
+        <v>737</v>
       </c>
       <c r="O14" t="n">
-        <v>610.529</v>
+        <v>776.7838</v>
       </c>
       <c r="P14" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="Q14" t="n">
-        <v>24.4212</v>
+        <v>21.5773</v>
       </c>
       <c r="R14" t="n">
         <v>185.8234</v>
@@ -3703,28 +3703,28 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02180451</v>
+        <v>0.02606516</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03239241</v>
+        <v>0.03410458</v>
       </c>
       <c r="Y14" t="n">
-        <v>1.6144</v>
+        <v>2.1526</v>
       </c>
       <c r="Z14" t="n">
-        <v>137</v>
+        <v>202</v>
       </c>
       <c r="AA14" t="n">
-        <v>390</v>
+        <v>540</v>
       </c>
       <c r="AB14" t="n">
-        <v>199.1665</v>
+        <v>235.2376</v>
       </c>
       <c r="AC14" t="n">
-        <v>799.4529</v>
+        <v>840.7666</v>
       </c>
       <c r="AD14" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AE14" t="n">
         <v>7</v>
@@ -3733,7 +3733,7 @@
         <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.0394</v>
+        <v>7.1602</v>
       </c>
     </row>
     <row r="15">
@@ -3771,22 +3771,22 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>350</v>
+        <v>393</v>
       </c>
       <c r="N15" t="n">
-        <v>975</v>
+        <v>1038</v>
       </c>
       <c r="O15" t="n">
-        <v>1160.193</v>
+        <v>3551.6522</v>
       </c>
       <c r="P15" t="n">
-        <v>46</v>
+        <v>148</v>
       </c>
       <c r="Q15" t="n">
-        <v>25.2216</v>
+        <v>23.9976</v>
       </c>
       <c r="R15" t="n">
         <v>259.2792</v>
@@ -3804,37 +3804,37 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.03619816</v>
+        <v>0.04064536</v>
       </c>
       <c r="X15" t="n">
-        <v>0.03927492</v>
+        <v>0.04181269</v>
       </c>
       <c r="Y15" t="n">
-        <v>3.8568</v>
+        <v>4.6282</v>
       </c>
       <c r="Z15" t="n">
-        <v>329</v>
+        <v>367</v>
       </c>
       <c r="AA15" t="n">
-        <v>731</v>
+        <v>852</v>
       </c>
       <c r="AB15" t="n">
-        <v>391.3209</v>
+        <v>438.0488</v>
       </c>
       <c r="AC15" t="n">
-        <v>1095.6783</v>
+        <v>1165.0631</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG15" t="n">
-        <v>6.8683</v>
+        <v>7.0702</v>
       </c>
     </row>
   </sheetData>

--- a/results/682_z23/5_quantification/682_z23_quantification.xlsx
+++ b/results/682_z23/5_quantification/682_z23_quantification.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -699,13 +699,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>8.6364</v>
+        <v>9.7273</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
       </c>
       <c r="E12" t="n">
-        <v>2.6181</v>
+        <v>2.8667</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -728,13 +728,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>348.3636</v>
+        <v>384.0909</v>
       </c>
       <c r="D13" t="n">
-        <v>352</v>
+        <v>386</v>
       </c>
       <c r="E13" t="n">
-        <v>87.1324</v>
+        <v>75.5201</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -757,13 +757,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>900.9091</v>
+        <v>947.0909</v>
       </c>
       <c r="D14" t="n">
-        <v>900</v>
+        <v>954</v>
       </c>
       <c r="E14" t="n">
-        <v>167.6451</v>
+        <v>167.1762</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -786,13 +786,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2403.5318</v>
+        <v>2655.5147</v>
       </c>
       <c r="D15" t="n">
-        <v>1927.3667</v>
+        <v>1936.0235</v>
       </c>
       <c r="E15" t="n">
-        <v>1454.4606</v>
+        <v>1396.0828</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -815,13 +815,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>112</v>
+        <v>124.5455</v>
       </c>
       <c r="D16" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="E16" t="n">
-        <v>71.8999</v>
+        <v>70.5455</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -844,13 +844,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>22.1506</v>
+        <v>21.8658</v>
       </c>
       <c r="D17" t="n">
-        <v>21.3106</v>
+        <v>21.3532</v>
       </c>
       <c r="E17" t="n">
-        <v>3.1481</v>
+        <v>2.5512</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1018,13 +1018,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.03965443</v>
+        <v>0.04338631</v>
       </c>
       <c r="D23" t="n">
-        <v>0.03724266</v>
+        <v>0.04138514</v>
       </c>
       <c r="E23" t="n">
-        <v>0.01151573</v>
+        <v>0.00814286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1047,13 +1047,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.0404533</v>
+        <v>0.04234058</v>
       </c>
       <c r="D24" t="n">
-        <v>0.03961422</v>
+        <v>0.04036254</v>
       </c>
       <c r="E24" t="n">
-        <v>0.00805999</v>
+        <v>0.00674093</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1076,13 +1076,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>4.0142</v>
+        <v>4.426</v>
       </c>
       <c r="D25" t="n">
-        <v>3.6416</v>
+        <v>4.2807</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4325</v>
+        <v>1.0458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -1105,13 +1105,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>302.2727</v>
+        <v>345.7273</v>
       </c>
       <c r="D26" t="n">
-        <v>292</v>
+        <v>327</v>
       </c>
       <c r="E26" t="n">
-        <v>101.1702</v>
+        <v>74.39230000000001</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1134,13 +1134,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>674.4545000000001</v>
+        <v>753</v>
       </c>
       <c r="D27" t="n">
-        <v>605</v>
+        <v>756</v>
       </c>
       <c r="E27" t="n">
-        <v>230.6085</v>
+        <v>185.9591</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1163,13 +1163,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>393.8255</v>
+        <v>433.334</v>
       </c>
       <c r="D28" t="n">
-        <v>392.7351</v>
+        <v>439.5341</v>
       </c>
       <c r="E28" t="n">
-        <v>98.2953</v>
+        <v>82.5219</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -1192,13 +1192,13 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1017.4285</v>
+        <v>1069.4368</v>
       </c>
       <c r="D29" t="n">
-        <v>1012.5656</v>
+        <v>1077.992</v>
       </c>
       <c r="E29" t="n">
-        <v>185.5464</v>
+        <v>181.9004</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -1221,13 +1221,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>8.3636</v>
+        <v>9.7273</v>
       </c>
       <c r="D30" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E30" t="n">
-        <v>1.9633</v>
+        <v>1.9022</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -1250,13 +1250,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>11.0909</v>
+        <v>11.9091</v>
       </c>
       <c r="D31" t="n">
         <v>12</v>
       </c>
       <c r="E31" t="n">
-        <v>2.7002</v>
+        <v>1.7581</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12.8182</v>
+        <v>13.3636</v>
       </c>
       <c r="D32" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E32" t="n">
-        <v>3.5726</v>
+        <v>3.1709</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -1299,29 +1299,87 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12.3636</v>
+      </c>
+      <c r="D33" t="n">
+        <v>10</v>
+      </c>
+      <c r="E33" t="n">
+        <v>10.4525</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="G33" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>loops, report only</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1285</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+      <c r="G34" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>width</t>
         </is>
       </c>
-      <c r="C33" t="n">
-        <v>7.1663</v>
-      </c>
-      <c r="D33" t="n">
-        <v>7.2028</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.3366</v>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="C35" t="n">
+        <v>7.1953</v>
+      </c>
+      <c r="D35" t="n">
+        <v>7.2449</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="F35" t="inlineStr">
         <is>
           <t>px</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="G35" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1336,7 +1394,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1393,7 +1451,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38363</v>
+        <v>40046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1413,7 +1471,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.03751105</v>
+        <v>0.03915667</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1433,7 +1491,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>880</v>
+        <v>938</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1453,7 +1511,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.00086046</v>
+        <v>0.00091717</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1513,7 +1571,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1533,7 +1591,7 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>145.8669</v>
+        <v>158.9127</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1553,7 +1611,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>17</v>
+        <v>18.5</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1573,7 +1631,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.0424887</v>
+        <v>0.04426246</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1593,7 +1651,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.03854185</v>
+        <v>0.03877941</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1670,7 +1728,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.03751105</v>
+        <v>0.03915667</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1690,11 +1748,71 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.03805861</v>
+        <v>0.03970424</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>px^-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>205</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.3824</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>share</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>edge_count</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>reported</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>2058</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>count</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1864,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7.7464</v>
+        <v>7.8311</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1826,7 +1944,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>36990</v>
+        <v>37218</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1969,7 +2087,7 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>652</v>
+        <v>740</v>
       </c>
     </row>
     <row r="9">
@@ -1984,7 +2102,7 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>21.2147</v>
+        <v>20.7958</v>
       </c>
     </row>
     <row r="10">
@@ -2014,7 +2132,7 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>44.4822</v>
+        <v>42.8519</v>
       </c>
     </row>
     <row r="12">
@@ -2029,7 +2147,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>50.0379</v>
+        <v>50.0455</v>
       </c>
     </row>
     <row r="13">
@@ -2044,7 +2162,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.4095</v>
+        <v>0.4041</v>
       </c>
     </row>
     <row r="14">
@@ -2059,7 +2177,7 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.5905</v>
+        <v>0.5959</v>
       </c>
     </row>
     <row r="15">
@@ -2136,7 +2254,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
@@ -2151,7 +2269,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="21">
@@ -2259,7 +2377,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AI15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2428,6 +2546,16 @@
           <t>ring_width_mean_r30_px</t>
         </is>
       </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>loop_count</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>loop_edge_share</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -2464,22 +2592,22 @@
         <v>1</v>
       </c>
       <c r="L2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M2" t="n">
-        <v>96</v>
+        <v>160</v>
       </c>
       <c r="N2" t="n">
-        <v>220</v>
+        <v>441</v>
       </c>
       <c r="O2" t="n">
-        <v>3079.4936</v>
+        <v>3034.6358</v>
       </c>
       <c r="P2" t="n">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="Q2" t="n">
-        <v>21.8404</v>
+        <v>20.2309</v>
       </c>
       <c r="R2" t="n">
         <v>105.1543</v>
@@ -2497,34 +2625,40 @@
         <v>0.597</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02593894</v>
+        <v>0.04323156</v>
       </c>
       <c r="X2" t="n">
-        <v>0.02165141</v>
+        <v>0.04340124</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.902</v>
+        <v>3.8039</v>
       </c>
       <c r="Z2" t="n">
-        <v>81</v>
+        <v>145</v>
       </c>
       <c r="AA2" t="n">
-        <v>151</v>
+        <v>372</v>
       </c>
       <c r="AB2" t="n">
-        <v>103.4264</v>
+        <v>175.468</v>
       </c>
       <c r="AC2" t="n">
-        <v>241.8234</v>
+        <v>488.3625</v>
       </c>
       <c r="AD2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>6</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>21</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.48</v>
       </c>
     </row>
     <row r="3">
@@ -2562,22 +2696,22 @@
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3" t="n">
-        <v>42</v>
+        <v>77</v>
       </c>
       <c r="N3" t="n">
-        <v>91</v>
+        <v>221</v>
       </c>
       <c r="O3" t="n">
-        <v>36.3137</v>
+        <v>1621.1758</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>83</v>
       </c>
       <c r="Q3" t="n">
-        <v>9.0784</v>
+        <v>19.5322</v>
       </c>
       <c r="R3" t="n">
         <v>132.8467</v>
@@ -2595,34 +2729,40 @@
         <v>0.5656</v>
       </c>
       <c r="W3" t="n">
-        <v>0.01135442</v>
+        <v>0.02081644</v>
       </c>
       <c r="X3" t="n">
-        <v>0.01183971</v>
+        <v>0.02875358</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.2582</v>
+        <v>3.011</v>
       </c>
       <c r="Z3" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="AA3" t="n">
-        <v>38</v>
+        <v>160</v>
       </c>
       <c r="AB3" t="n">
-        <v>43.1421</v>
+        <v>87.01220000000001</v>
       </c>
       <c r="AC3" t="n">
-        <v>98.7696</v>
+        <v>241.196</v>
       </c>
       <c r="AD3" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE3" t="n">
         <v>1</v>
       </c>
-      <c r="AE3" t="n">
-        <v>0</v>
-      </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>3</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>13</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.5422</v>
       </c>
     </row>
     <row r="4">
@@ -2663,19 +2803,19 @@
         <v>8</v>
       </c>
       <c r="M4" t="n">
-        <v>329</v>
+        <v>386</v>
       </c>
       <c r="N4" t="n">
-        <v>752</v>
+        <v>811</v>
       </c>
       <c r="O4" t="n">
-        <v>1927.3667</v>
+        <v>1936.0235</v>
       </c>
       <c r="P4" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="Q4" t="n">
-        <v>20.0767</v>
+        <v>19.1685</v>
       </c>
       <c r="R4" t="n">
         <v>219.6812</v>
@@ -2693,37 +2833,43 @@
         <v>0.9689</v>
       </c>
       <c r="W4" t="n">
-        <v>0.0366533</v>
+        <v>0.04300357</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0363022</v>
+        <v>0.03915037</v>
       </c>
       <c r="Y4" t="n">
         <v>3.6416</v>
       </c>
       <c r="Z4" t="n">
-        <v>190</v>
+        <v>300</v>
       </c>
       <c r="AA4" t="n">
-        <v>462</v>
+        <v>516</v>
       </c>
       <c r="AB4" t="n">
-        <v>366.9066</v>
+        <v>428.463</v>
       </c>
       <c r="AC4" t="n">
-        <v>831.9554000000001</v>
+        <v>895.5118</v>
       </c>
       <c r="AD4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AE4" t="n">
         <v>12</v>
       </c>
       <c r="AF4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG4" t="n">
-        <v>6.7412</v>
+        <v>7.2461</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.4554</v>
       </c>
     </row>
     <row r="5">
@@ -2761,22 +2907,22 @@
         <v>0</v>
       </c>
       <c r="L5" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M5" t="n">
-        <v>461</v>
+        <v>440</v>
       </c>
       <c r="N5" t="n">
-        <v>1086</v>
+        <v>1067</v>
       </c>
       <c r="O5" t="n">
-        <v>5431.624</v>
+        <v>5400.0676</v>
       </c>
       <c r="P5" t="n">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="Q5" t="n">
-        <v>20.2673</v>
+        <v>19.9264</v>
       </c>
       <c r="R5" t="n">
         <v>210.2437</v>
@@ -2794,28 +2940,28 @@
         <v>1</v>
       </c>
       <c r="W5" t="n">
-        <v>0.0541652</v>
+        <v>0.0516978</v>
       </c>
       <c r="X5" t="n">
-        <v>0.04807224</v>
+        <v>0.0472312</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7077</v>
+        <v>4.2807</v>
       </c>
       <c r="Z5" t="n">
-        <v>450</v>
+        <v>428</v>
       </c>
       <c r="AA5" t="n">
-        <v>1055</v>
+        <v>1011</v>
       </c>
       <c r="AB5" t="n">
-        <v>531.5168</v>
+        <v>504.3747</v>
       </c>
       <c r="AC5" t="n">
-        <v>1247.1585</v>
+        <v>1222.4306</v>
       </c>
       <c r="AD5" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AE5" t="n">
         <v>13</v>
@@ -2824,7 +2970,13 @@
         <v>12</v>
       </c>
       <c r="AG5" t="n">
-        <v>7.2028</v>
+        <v>6.9019</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.4834</v>
       </c>
     </row>
     <row r="6">
@@ -2862,22 +3014,22 @@
         <v>0</v>
       </c>
       <c r="L6" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="M6" t="n">
-        <v>352</v>
+        <v>470</v>
       </c>
       <c r="N6" t="n">
-        <v>922</v>
+        <v>1116</v>
       </c>
       <c r="O6" t="n">
-        <v>3128.1698</v>
+        <v>4334.8237</v>
       </c>
       <c r="P6" t="n">
-        <v>156</v>
+        <v>206</v>
       </c>
       <c r="Q6" t="n">
-        <v>20.0524</v>
+        <v>21.0428</v>
       </c>
       <c r="R6" t="n">
         <v>335.4214</v>
@@ -2895,37 +3047,43 @@
         <v>1</v>
       </c>
       <c r="W6" t="n">
-        <v>0.02890458</v>
+        <v>0.03859419</v>
       </c>
       <c r="X6" t="n">
-        <v>0.03080315</v>
+        <v>0.03728451</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.6832</v>
+        <v>4.472</v>
       </c>
       <c r="Z6" t="n">
-        <v>325</v>
+        <v>432</v>
       </c>
       <c r="AA6" t="n">
-        <v>605</v>
+        <v>790</v>
       </c>
       <c r="AB6" t="n">
-        <v>392.7351</v>
+        <v>518.5046</v>
       </c>
       <c r="AC6" t="n">
-        <v>1022.4234</v>
+        <v>1237.1341</v>
       </c>
       <c r="AD6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AE6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AF6" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="AG6" t="n">
-        <v>7.4414</v>
+        <v>7.6645</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.3495</v>
       </c>
     </row>
     <row r="7">
@@ -2963,22 +3121,22 @@
         <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M7" t="n">
-        <v>261</v>
+        <v>298</v>
       </c>
       <c r="N7" t="n">
-        <v>743</v>
+        <v>790</v>
       </c>
       <c r="O7" t="n">
-        <v>1344.8276</v>
+        <v>2560.8023</v>
       </c>
       <c r="P7" t="n">
-        <v>62</v>
+        <v>122</v>
       </c>
       <c r="Q7" t="n">
-        <v>21.6908</v>
+        <v>20.9902</v>
       </c>
       <c r="R7" t="n">
         <v>167.2376</v>
@@ -2996,37 +3154,43 @@
         <v>1</v>
       </c>
       <c r="W7" t="n">
-        <v>0.03486974</v>
+        <v>0.03981296</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0360995</v>
+        <v>0.03838305</v>
       </c>
       <c r="Y7" t="n">
-        <v>4.1857</v>
+        <v>3.5877</v>
       </c>
       <c r="Z7" t="n">
-        <v>224</v>
+        <v>281</v>
       </c>
       <c r="AA7" t="n">
-        <v>403</v>
+        <v>622</v>
       </c>
       <c r="AB7" t="n">
-        <v>301.8356</v>
+        <v>346.6346</v>
       </c>
       <c r="AC7" t="n">
-        <v>856.7372</v>
+        <v>913.193</v>
       </c>
       <c r="AD7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>9</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>8</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>7.8485</v>
+      </c>
+      <c r="AH7" t="n">
         <v>7</v>
       </c>
-      <c r="AE7" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>7.6091</v>
+      <c r="AI7" t="n">
+        <v>0.2541</v>
       </c>
     </row>
     <row r="8">
@@ -3064,22 +3228,22 @@
         <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M8" t="n">
-        <v>369</v>
+        <v>392</v>
       </c>
       <c r="N8" t="n">
-        <v>900</v>
+        <v>925</v>
       </c>
       <c r="O8" t="n">
-        <v>3942.4562</v>
+        <v>4122.7527</v>
       </c>
       <c r="P8" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="Q8" t="n">
-        <v>21.3106</v>
+        <v>21.4727</v>
       </c>
       <c r="R8" t="n">
         <v>243.5219</v>
@@ -3097,25 +3261,25 @@
         <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0.03895693</v>
+        <v>0.04138514</v>
       </c>
       <c r="X8" t="n">
-        <v>0.04080522</v>
+        <v>0.0419387</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.8745</v>
+        <v>4.1064</v>
       </c>
       <c r="Z8" t="n">
-        <v>292</v>
+        <v>316</v>
       </c>
       <c r="AA8" t="n">
-        <v>602</v>
+        <v>626</v>
       </c>
       <c r="AB8" t="n">
-        <v>411.1493</v>
+        <v>439.5341</v>
       </c>
       <c r="AC8" t="n">
-        <v>1012.5656</v>
+        <v>1043.3646</v>
       </c>
       <c r="AD8" t="n">
         <v>9</v>
@@ -3127,7 +3291,13 @@
         <v>12</v>
       </c>
       <c r="AG8" t="n">
-        <v>7.2722</v>
+        <v>7.2449</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.4688</v>
       </c>
     </row>
     <row r="9">
@@ -3165,22 +3335,22 @@
         <v>0</v>
       </c>
       <c r="L9" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="M9" t="n">
-        <v>490</v>
+        <v>460</v>
       </c>
       <c r="N9" t="n">
-        <v>1003</v>
+        <v>980</v>
       </c>
       <c r="O9" t="n">
-        <v>2452.0256</v>
+        <v>1776.4255</v>
       </c>
       <c r="P9" t="n">
-        <v>116</v>
+        <v>92</v>
       </c>
       <c r="Q9" t="n">
-        <v>21.1382</v>
+        <v>19.309</v>
       </c>
       <c r="R9" t="n">
         <v>167.9239</v>
@@ -3198,25 +3368,25 @@
         <v>1</v>
       </c>
       <c r="W9" t="n">
-        <v>0.06667574</v>
+        <v>0.06259355</v>
       </c>
       <c r="X9" t="n">
-        <v>0.05713472</v>
+        <v>0.05582455</v>
       </c>
       <c r="Y9" t="n">
-        <v>7.1461</v>
+        <v>5.9551</v>
       </c>
       <c r="Z9" t="n">
-        <v>478</v>
+        <v>448</v>
       </c>
       <c r="AA9" t="n">
-        <v>976</v>
+        <v>951</v>
       </c>
       <c r="AB9" t="n">
-        <v>552.8183</v>
+        <v>520.1615</v>
       </c>
       <c r="AC9" t="n">
-        <v>1123.7372</v>
+        <v>1099.6661</v>
       </c>
       <c r="AD9" t="n">
         <v>11</v>
@@ -3228,7 +3398,13 @@
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>7.4172</v>
+        <v>7.3791</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>10</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.4022</v>
       </c>
     </row>
     <row r="10">
@@ -3269,19 +3445,19 @@
         <v>10</v>
       </c>
       <c r="M10" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="N10" t="n">
-        <v>785</v>
+        <v>815</v>
       </c>
       <c r="O10" t="n">
-        <v>1237.6072</v>
+        <v>1273.4773</v>
       </c>
       <c r="P10" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="Q10" t="n">
-        <v>22.9187</v>
+        <v>24.0279</v>
       </c>
       <c r="R10" t="n">
         <v>282.8944</v>
@@ -3299,37 +3475,43 @@
         <v>0.7462</v>
       </c>
       <c r="W10" t="n">
-        <v>0.03756626</v>
+        <v>0.04044711</v>
       </c>
       <c r="X10" t="n">
-        <v>0.04060625</v>
+        <v>0.04215808</v>
       </c>
       <c r="Y10" t="n">
         <v>3.5349</v>
       </c>
       <c r="Z10" t="n">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="AA10" t="n">
-        <v>619</v>
+        <v>547</v>
       </c>
       <c r="AB10" t="n">
-        <v>366.1493</v>
+        <v>400.1909</v>
       </c>
       <c r="AC10" t="n">
-        <v>879.1686</v>
+        <v>919.2102</v>
       </c>
       <c r="AD10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
       </c>
       <c r="AG10" t="n">
-        <v>7.5147</v>
+        <v>7.4606</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.1321</v>
       </c>
     </row>
     <row r="11">
@@ -3367,22 +3549,22 @@
         <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M11" t="n">
-        <v>398</v>
+        <v>471</v>
       </c>
       <c r="N11" t="n">
-        <v>1191</v>
+        <v>1274</v>
       </c>
       <c r="O11" t="n">
-        <v>1534.3128</v>
+        <v>3081.5962</v>
       </c>
       <c r="P11" t="n">
-        <v>67</v>
+        <v>135</v>
       </c>
       <c r="Q11" t="n">
-        <v>22.9002</v>
+        <v>22.8266</v>
       </c>
       <c r="R11" t="n">
         <v>263.4802</v>
@@ -3400,37 +3582,43 @@
         <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0.03912702</v>
+        <v>0.04630358</v>
       </c>
       <c r="X11" t="n">
-        <v>0.04850929</v>
+        <v>0.05188987</v>
       </c>
       <c r="Y11" t="n">
-        <v>3.4158</v>
+        <v>3.0363</v>
       </c>
       <c r="Z11" t="n">
-        <v>345</v>
+        <v>416</v>
       </c>
       <c r="AA11" t="n">
-        <v>889</v>
+        <v>1062</v>
       </c>
       <c r="AB11" t="n">
-        <v>448.1198</v>
+        <v>525.7767</v>
       </c>
       <c r="AC11" t="n">
-        <v>1336.5605</v>
+        <v>1428.7027</v>
       </c>
       <c r="AD11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="AE11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF11" t="n">
         <v>19</v>
       </c>
       <c r="AG11" t="n">
-        <v>7.5386</v>
+        <v>7.3243</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>15</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.437</v>
       </c>
     </row>
     <row r="12">
@@ -3468,22 +3656,22 @@
         <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M12" t="n">
-        <v>249</v>
+        <v>289</v>
       </c>
       <c r="N12" t="n">
-        <v>659</v>
+        <v>706</v>
       </c>
       <c r="O12" t="n">
-        <v>1140.4133</v>
+        <v>1835.2266</v>
       </c>
       <c r="P12" t="n">
-        <v>37</v>
+        <v>66</v>
       </c>
       <c r="Q12" t="n">
-        <v>30.822</v>
+        <v>27.8065</v>
       </c>
       <c r="R12" t="n">
         <v>174.5097</v>
@@ -3501,37 +3689,43 @@
         <v>1</v>
       </c>
       <c r="W12" t="n">
-        <v>0.032893</v>
+        <v>0.03817701</v>
       </c>
       <c r="X12" t="n">
-        <v>0.03172845</v>
+        <v>0.03399133</v>
       </c>
       <c r="Y12" t="n">
-        <v>3.4382</v>
+        <v>4.0112</v>
       </c>
       <c r="Z12" t="n">
-        <v>190</v>
+        <v>248</v>
       </c>
       <c r="AA12" t="n">
-        <v>412</v>
+        <v>572</v>
       </c>
       <c r="AB12" t="n">
-        <v>282.865</v>
+        <v>327.1787</v>
       </c>
       <c r="AC12" t="n">
-        <v>763.6955</v>
+        <v>815.0092</v>
       </c>
       <c r="AD12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AF12" t="n">
         <v>10</v>
       </c>
       <c r="AG12" t="n">
-        <v>6.6908</v>
+        <v>6.9399</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.2424</v>
       </c>
     </row>
     <row r="13">
@@ -3569,22 +3763,22 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="M13" t="n">
-        <v>322</v>
+        <v>385</v>
       </c>
       <c r="N13" t="n">
-        <v>879</v>
+        <v>954</v>
       </c>
       <c r="O13" t="n">
-        <v>1209.2174</v>
+        <v>1387.9575</v>
       </c>
       <c r="P13" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="Q13" t="n">
-        <v>19.8232</v>
+        <v>21.3532</v>
       </c>
       <c r="R13" t="n">
         <v>210.1665</v>
@@ -3602,37 +3796,43 @@
         <v>1</v>
       </c>
       <c r="W13" t="n">
-        <v>0.03724266</v>
+        <v>0.04452926</v>
       </c>
       <c r="X13" t="n">
-        <v>0.03961422</v>
+        <v>0.04299428</v>
       </c>
       <c r="Y13" t="n">
-        <v>4.2823</v>
+        <v>6.6614</v>
       </c>
       <c r="Z13" t="n">
-        <v>262</v>
+        <v>327</v>
       </c>
       <c r="AA13" t="n">
-        <v>623</v>
+        <v>768</v>
       </c>
       <c r="AB13" t="n">
-        <v>370.8478</v>
+        <v>443.9605</v>
       </c>
       <c r="AC13" t="n">
-        <v>991.0509</v>
+        <v>1077.992</v>
       </c>
       <c r="AD13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AE13" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AF13" t="n">
         <v>17</v>
       </c>
       <c r="AG13" t="n">
-        <v>6.6855</v>
+        <v>6.4529</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0.2923</v>
       </c>
     </row>
     <row r="14">
@@ -3670,22 +3870,22 @@
         <v>0</v>
       </c>
       <c r="L14" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="M14" t="n">
-        <v>208</v>
+        <v>255</v>
       </c>
       <c r="N14" t="n">
-        <v>737</v>
+        <v>793</v>
       </c>
       <c r="O14" t="n">
-        <v>776.7838</v>
+        <v>1453.526</v>
       </c>
       <c r="P14" t="n">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="Q14" t="n">
-        <v>21.5773</v>
+        <v>21.6944</v>
       </c>
       <c r="R14" t="n">
         <v>185.8234</v>
@@ -3703,37 +3903,43 @@
         <v>1</v>
       </c>
       <c r="W14" t="n">
-        <v>0.02606516</v>
+        <v>0.03195489</v>
       </c>
       <c r="X14" t="n">
-        <v>0.03410458</v>
+        <v>0.03669597</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.1526</v>
+        <v>4.3052</v>
       </c>
       <c r="Z14" t="n">
-        <v>202</v>
+        <v>253</v>
       </c>
       <c r="AA14" t="n">
-        <v>540</v>
+        <v>609</v>
       </c>
       <c r="AB14" t="n">
-        <v>235.2376</v>
+        <v>289.6934</v>
       </c>
       <c r="AC14" t="n">
-        <v>840.7666</v>
+        <v>907.2935</v>
       </c>
       <c r="AD14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AF14" t="n">
         <v>11</v>
       </c>
       <c r="AG14" t="n">
-        <v>7.1602</v>
+        <v>7.1906</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0.2985</v>
       </c>
     </row>
     <row r="15">
@@ -3774,19 +3980,19 @@
         <v>12</v>
       </c>
       <c r="M15" t="n">
-        <v>393</v>
+        <v>379</v>
       </c>
       <c r="N15" t="n">
-        <v>1038</v>
+        <v>1002</v>
       </c>
       <c r="O15" t="n">
-        <v>3551.6522</v>
+        <v>1321.46</v>
       </c>
       <c r="P15" t="n">
-        <v>148</v>
+        <v>53</v>
       </c>
       <c r="Q15" t="n">
-        <v>23.9976</v>
+        <v>24.9332</v>
       </c>
       <c r="R15" t="n">
         <v>259.2792</v>
@@ -3804,37 +4010,43 @@
         <v>1</v>
       </c>
       <c r="W15" t="n">
-        <v>0.04064536</v>
+        <v>0.03919744</v>
       </c>
       <c r="X15" t="n">
-        <v>0.04181269</v>
+        <v>0.04036254</v>
       </c>
       <c r="Y15" t="n">
         <v>4.6282</v>
       </c>
       <c r="Z15" t="n">
-        <v>367</v>
+        <v>354</v>
       </c>
       <c r="AA15" t="n">
-        <v>852</v>
+        <v>756</v>
       </c>
       <c r="AB15" t="n">
-        <v>438.0488</v>
+        <v>422.3919</v>
       </c>
       <c r="AC15" t="n">
-        <v>1165.0631</v>
+        <v>1123.5067</v>
       </c>
       <c r="AD15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
+        <v>12</v>
+      </c>
+      <c r="AF15" t="n">
         <v>14</v>
       </c>
-      <c r="AF15" t="n">
-        <v>15</v>
-      </c>
       <c r="AG15" t="n">
-        <v>7.0702</v>
+        <v>6.9559</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0.0566</v>
       </c>
     </row>
   </sheetData>
